--- a/Dataset_0/4_Integration_results/Stats_table_final.xlsx
+++ b/Dataset_0/4_Integration_results/Stats_table_final.xlsx
@@ -110,7 +110,7 @@
     <t xml:space="preserve">DM ∩ DE DM down (padj)</t>
   </si>
   <si>
-    <t xml:space="preserve">M ∩ DE vs All DM down (padj)</t>
+    <t xml:space="preserve">DM ∩ DE vs All DM down (padj)</t>
   </si>
   <si>
     <t xml:space="preserve">Hypo-up (padj)</t>

--- a/Dataset_0/4_Integration_results/Stats_table_final.xlsx
+++ b/Dataset_0/4_Integration_results/Stats_table_final.xlsx
@@ -101,7 +101,7 @@
     <t xml:space="preserve">DM ∩ DE DM up (padj)</t>
   </si>
   <si>
-    <t xml:space="preserve">M ∩ DE vs All DM up (padj)</t>
+    <t xml:space="preserve">DM ∩ DE vs All DM up (padj)</t>
   </si>
   <si>
     <t xml:space="preserve">All DM down (padj)</t>
@@ -918,19 +918,19 @@
         <v>27</v>
       </c>
       <c r="B23" t="n">
-        <v>0.400479319478628</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.792848988380877</v>
+        <v>0.859775227366615</v>
       </c>
       <c r="E23" t="n">
-        <v>0.567447326525889</v>
+        <v>0.368666748711692</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0.792999336680581</v>
       </c>
     </row>
     <row r="24">
@@ -938,19 +938,19 @@
         <v>28</v>
       </c>
       <c r="B24" t="n">
-        <v>1</v>
+        <v>0.400479319478628</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.859775227366615</v>
+        <v>0.792848988380877</v>
       </c>
       <c r="E24" t="n">
-        <v>0.368666748711692</v>
+        <v>0.567447326525889</v>
       </c>
       <c r="F24" t="n">
-        <v>0.792999336680581</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -978,19 +978,19 @@
         <v>30</v>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0.798081628102821</v>
       </c>
       <c r="C26" t="n">
-        <v>0.666442038305799</v>
+        <v>0.715280325672026</v>
       </c>
       <c r="D26" t="n">
         <v>0.792848988380877</v>
       </c>
       <c r="E26" t="n">
-        <v>0.935684034475001</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>0.429869892320491</v>
+        <v>0.817486323110491</v>
       </c>
     </row>
     <row r="27">
@@ -998,19 +998,19 @@
         <v>31</v>
       </c>
       <c r="B27" t="n">
-        <v>0.798081628102821</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.715280325672026</v>
+        <v>0.666442038305799</v>
       </c>
       <c r="D27" t="n">
         <v>0.792848988380877</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0.935684034475001</v>
       </c>
       <c r="F27" t="n">
-        <v>0.817486323110491</v>
+        <v>0.429869892320491</v>
       </c>
     </row>
     <row r="28">

--- a/Dataset_0/4_Integration_results/Stats_table_final.xlsx
+++ b/Dataset_0/4_Integration_results/Stats_table_final.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">metric</t>
   </si>
@@ -111,18 +111,6 @@
   </si>
   <si>
     <t xml:space="preserve">DM ∩ DE vs All DM down (padj)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypo-up (padj)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypo-down (padj)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hyper-up (padj)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hyper-down (padj)</t>
   </si>
   <si>
     <t xml:space="preserve">meth Spear (rho)</t>
@@ -898,19 +886,19 @@
         <v>26</v>
       </c>
       <c r="B22" t="n">
-        <v>0.946262755500886</v>
+        <v>0.925234694267533</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0.999999996943972</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0798878996677227</v>
+        <v>0.09764076626055</v>
       </c>
       <c r="E22" t="n">
-        <v>0.117493652250103</v>
+        <v>0.143603352750126</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0472696556053571</v>
+        <v>0.0519966211658929</v>
       </c>
     </row>
     <row r="23">
@@ -918,19 +906,19 @@
         <v>27</v>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>0.999999999986116</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0.999999996943972</v>
       </c>
       <c r="D23" t="n">
-        <v>0.859775227366615</v>
+        <v>0.770613351936003</v>
       </c>
       <c r="E23" t="n">
-        <v>0.368666748711692</v>
+        <v>0.405533423582862</v>
       </c>
       <c r="F23" t="n">
-        <v>0.792999336680581</v>
+        <v>0.747685088870262</v>
       </c>
     </row>
     <row r="24">
@@ -938,19 +926,19 @@
         <v>28</v>
       </c>
       <c r="B24" t="n">
-        <v>0.400479319478628</v>
+        <v>0.440527251426491</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0.999999996943972</v>
       </c>
       <c r="D24" t="n">
-        <v>0.792848988380877</v>
+        <v>0.726778239349138</v>
       </c>
       <c r="E24" t="n">
-        <v>0.567447326525889</v>
+        <v>0.535021765010124</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0.901380608450031</v>
       </c>
     </row>
     <row r="25">
@@ -958,19 +946,19 @@
         <v>29</v>
       </c>
       <c r="B25" t="n">
-        <v>0.0000000000906986988302459</v>
+        <v>0.000000000133024758284361</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0000000172938148427376</v>
+        <v>0.0000000253642617693485</v>
       </c>
       <c r="D25" t="n">
-        <v>0.00008398828601998</v>
+        <v>0.000123182819495971</v>
       </c>
       <c r="E25" t="n">
-        <v>0.000000199255960676204</v>
+        <v>0.000000292242075658433</v>
       </c>
       <c r="F25" t="n">
-        <v>0.00000275185523349412</v>
+        <v>0.00000403605434245805</v>
       </c>
     </row>
     <row r="26">
@@ -978,19 +966,19 @@
         <v>30</v>
       </c>
       <c r="B26" t="n">
-        <v>0.798081628102821</v>
+        <v>0.81936380485223</v>
       </c>
       <c r="C26" t="n">
-        <v>0.715280325672026</v>
+        <v>0.786808358239229</v>
       </c>
       <c r="D26" t="n">
-        <v>0.792848988380877</v>
+        <v>0.726778239349138</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0.950710454385906</v>
       </c>
       <c r="F26" t="n">
-        <v>0.817486323110491</v>
+        <v>0.749362462851283</v>
       </c>
     </row>
     <row r="27">
@@ -998,19 +986,19 @@
         <v>31</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0.999999999986116</v>
       </c>
       <c r="C27" t="n">
-        <v>0.666442038305799</v>
+        <v>0.786808358239229</v>
       </c>
       <c r="D27" t="n">
-        <v>0.792848988380877</v>
+        <v>0.726778239349138</v>
       </c>
       <c r="E27" t="n">
-        <v>0.935684034475001</v>
+        <v>0.838650134603519</v>
       </c>
       <c r="F27" t="n">
-        <v>0.429869892320491</v>
+        <v>0.441333089449037</v>
       </c>
     </row>
     <row r="28">
@@ -1018,19 +1006,19 @@
         <v>32</v>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>0.999999999986116</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0.999999996943972</v>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>0.999986623121019</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0.999999965244419</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0.999999498709064</v>
       </c>
     </row>
     <row r="29">
@@ -1038,19 +1026,19 @@
         <v>33</v>
       </c>
       <c r="B29" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000433255033228847</v>
+        <v>-0.409109016653763</v>
       </c>
       <c r="C29" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000348185610891921</v>
+        <v>-0.47110684949761</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000125069586983971</v>
+        <v>-0.485683401958857</v>
       </c>
       <c r="E29" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000279617285458204</v>
+        <v>-0.392921679884139</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000893875118589009</v>
+        <v>-0.385243661772262</v>
       </c>
     </row>
     <row r="30">
@@ -1058,19 +1046,19 @@
         <v>34</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000186498912036999</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0.000000000000000000000000000000000000000000000000000526094560387973</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>0.00000000000000000000000000000000000000000000000000103784061611252</v>
       </c>
     </row>
     <row r="31">
@@ -1078,19 +1066,19 @@
         <v>35</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>1430</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>491</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>1046</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>855</v>
       </c>
     </row>
     <row r="32">
@@ -1098,19 +1086,19 @@
         <v>36</v>
       </c>
       <c r="B32" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000433255033228847</v>
+        <v>0.0781984421777209</v>
       </c>
       <c r="C32" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000348185610891921</v>
+        <v>0.999999996943972</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000125069586983971</v>
+        <v>0.961456364014843</v>
       </c>
       <c r="E32" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000279617285458204</v>
+        <v>0.454587518659965</v>
       </c>
       <c r="F32" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000893875118589009</v>
+        <v>0.000140315517513915</v>
       </c>
     </row>
     <row r="33">
@@ -1118,19 +1106,19 @@
         <v>37</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.409109016653763</v>
+        <v>0.0000713058721796288</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.47110684949761</v>
+        <v>-0.0102155146340272</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.485683401958857</v>
+        <v>-0.0271866845316231</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.392921679884139</v>
+        <v>-0.0221090527426069</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.385243661772262</v>
+        <v>-0.0219718589844441</v>
       </c>
     </row>
     <row r="34">
@@ -1138,19 +1126,19 @@
         <v>38</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>0.999999999986116</v>
       </c>
       <c r="C34" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000847722327440902</v>
+        <v>0.999999996943972</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>0.726778239349138</v>
       </c>
       <c r="E34" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000239133891085442</v>
+        <v>0.454587518659965</v>
       </c>
       <c r="F34" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000471745734596598</v>
+        <v>0.443116308941216</v>
       </c>
     </row>
     <row r="35">
@@ -1158,19 +1146,19 @@
         <v>39</v>
       </c>
       <c r="B35" t="n">
-        <v>1430</v>
+        <v>0.00109301987711543</v>
       </c>
       <c r="C35" t="n">
-        <v>491</v>
+        <v>-0.000000594624275686981</v>
       </c>
       <c r="D35" t="n">
-        <v>75</v>
+        <v>-0.021661755396939</v>
       </c>
       <c r="E35" t="n">
-        <v>1046</v>
+        <v>-0.00892263371907077</v>
       </c>
       <c r="F35" t="n">
-        <v>855</v>
+        <v>-0.00466743184913102</v>
       </c>
     </row>
     <row r="36">
@@ -1178,99 +1166,19 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>0.0639805435999535</v>
+        <v>0.999999999986116</v>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>0.999999996943972</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>0.726778239349138</v>
       </c>
       <c r="E36" t="n">
-        <v>0.464919053174964</v>
+        <v>0.838650134603519</v>
       </c>
       <c r="F36" t="n">
-        <v>0.000114803605238657</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" t="n">
-        <v>0.0000713058721796288</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.0102155146340272</v>
-      </c>
-      <c r="D37" t="n">
-        <v>-0.0271866845316231</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-0.0221090527426069</v>
-      </c>
-      <c r="F37" t="n">
-        <v>-0.0219718589844441</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="n">
-        <v>1</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0.792848988380877</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.464919053174964</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.453187134144426</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39" t="n">
-        <v>0.00109301987711543</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.000000594624275686981</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-0.021661755396939</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-0.00892263371907077</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-0.00466743184913102</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>44</v>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.792848988380877</v>
-      </c>
-      <c r="E40" t="n">
-        <v>0.935684034475001</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1</v>
+        <v>0.901380608450031</v>
       </c>
     </row>
   </sheetData>
